--- a/Inputs/_MasterFiles/FTT-GMP/FTT-GMP-4x1_2026_S0.xlsx
+++ b/Inputs/_MasterFiles/FTT-GMP/FTT-GMP-4x1_2026_S0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofexeteruk-my.sharepoint.com/personal/ae476_exeter_ac_uk/Documents/Documents/GitHub/FTT_StandAlone_GMP/Inputs/_MasterFiles/FTT-GMP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="288" documentId="8_{13BF6B7A-2A1B-4BF6-9A13-F59AE887C3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{587DDFC8-51D4-4AE2-889B-A64646199D06}"/>
+  <xr:revisionPtr revIDLastSave="317" documentId="8_{13BF6B7A-2A1B-4BF6-9A13-F59AE887C3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3870FC59-DEF5-4775-B96D-CDC5FE0C4F47}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="767" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1120" yWindow="1730" windowWidth="9600" windowHeight="5210" tabRatio="767" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="87">
   <si>
     <t>File name</t>
   </si>
@@ -257,9 +257,6 @@
     <t xml:space="preserve">std </t>
   </si>
   <si>
-    <t>O&amp;M (fixed)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lifetime </t>
   </si>
   <si>
@@ -269,9 +266,6 @@
     <t xml:space="preserve">Capture/production rates  </t>
   </si>
   <si>
-    <t>O&amp;M (variable)</t>
-  </si>
-  <si>
     <t>Baseline capacity</t>
   </si>
   <si>
@@ -279,6 +273,33 @@
   </si>
   <si>
     <t>Lead time</t>
+  </si>
+  <si>
+    <t>CAPEX</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>(£/tCO2 or £/kg H2)</t>
+  </si>
+  <si>
+    <t>O&amp;M</t>
+  </si>
+  <si>
+    <t>Non-energy operating costs (e.g. insurance, taxes, wages, sorbents etc.)</t>
+  </si>
+  <si>
+    <t>Discount rate</t>
+  </si>
+  <si>
+    <t>Storage costs</t>
+  </si>
+  <si>
+    <t>CCS</t>
+  </si>
+  <si>
+    <t>%</t>
   </si>
 </sst>
 </file>
@@ -1485,23 +1506,24 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF37CFFF"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="41.08984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="41.08984375" customWidth="1"/>
-    <col min="6" max="6" width="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>51</v>
       </c>
@@ -1515,13 +1537,16 @@
         <v>63</v>
       </c>
       <c r="F1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" t="s">
         <v>51</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1535,13 +1560,16 @@
         <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2">
+        <v>80</v>
+      </c>
+      <c r="F2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1558,11 +1586,11 @@
       <c r="E3" t="s">
         <v>64</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1574,16 +1602,19 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>64</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1600,35 +1631,47 @@
       <c r="E5" t="s">
         <v>64</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
       <c r="C6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6">
+        <v>72</v>
+      </c>
+      <c r="E6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="C7">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7">
+        <v>77</v>
+      </c>
+      <c r="E7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="C8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1637,164 +1680,167 @@
         <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8">
+        <v>66</v>
+      </c>
+      <c r="G8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="C9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9">
+        <v>59</v>
+      </c>
+      <c r="G9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="C10">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="C11">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11">
+        <v>67</v>
+      </c>
+      <c r="G11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="C12">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12">
+        <v>60</v>
+      </c>
+      <c r="G12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:8">
       <c r="C13">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13">
+        <v>61</v>
+      </c>
+      <c r="G13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:8">
       <c r="C14">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14">
+        <v>69</v>
+      </c>
+      <c r="G14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:8">
       <c r="C15">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15">
+        <v>83</v>
+      </c>
+      <c r="E15" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:8">
       <c r="C16">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16">
+        <v>84</v>
+      </c>
+      <c r="E16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="6:6">
-      <c r="F17">
+    <row r="17" spans="7:7">
+      <c r="G17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="6:6">
-      <c r="F18">
+    <row r="18" spans="7:7">
+      <c r="G18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="6:6">
-      <c r="F19">
+    <row r="19" spans="7:7">
+      <c r="G19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="6:6">
-      <c r="F20">
+    <row r="20" spans="7:7">
+      <c r="G20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="6:6">
-      <c r="F21">
+    <row r="21" spans="7:7">
+      <c r="G21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="6:6">
-      <c r="F22">
+    <row r="22" spans="7:7">
+      <c r="G22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="6:6">
-      <c r="F23">
+    <row r="23" spans="7:7">
+      <c r="G23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="6:6">
-      <c r="F24">
+    <row r="24" spans="7:7">
+      <c r="G24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="6:6">
-      <c r="F25">
+    <row r="25" spans="7:7">
+      <c r="G25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="6:6">
-      <c r="F26">
+    <row r="26" spans="7:7">
+      <c r="G26">
         <v>25</v>
       </c>
     </row>
@@ -1949,54 +1995,54 @@
       </c>
       <c r="E5" s="26" t="str">
         <f>Titles!$D$4</f>
-        <v>O&amp;M (fixed)</v>
-      </c>
-      <c r="F5" s="26" t="str">
-        <f>Titles!$D$5</f>
-        <v xml:space="preserve">std </v>
-      </c>
-      <c r="G5" s="26" t="str">
+        <v>O&amp;M</v>
+      </c>
+      <c r="F5" s="26" t="e">
+        <f>Titles!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="G5" s="26" t="e">
+        <f>Titles!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H5" s="26" t="e">
+        <f>Titles!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I5" s="26" t="str">
         <f>Titles!$D$6</f>
-        <v>O&amp;M (variable)</v>
-      </c>
-      <c r="H5" s="26" t="str">
-        <f>Titles!$D$7</f>
-        <v xml:space="preserve">std </v>
-      </c>
-      <c r="I5" s="26" t="str">
-        <f>Titles!$D$8</f>
         <v xml:space="preserve">Lifetime </v>
       </c>
       <c r="J5" s="26" t="str">
+        <f>Titles!$D7</f>
+        <v>Lead time</v>
+      </c>
+      <c r="K5" s="26" t="str">
+        <f>Titles!$D8</f>
+        <v xml:space="preserve">Efficiency </v>
+      </c>
+      <c r="L5" s="26" t="str">
         <f>Titles!$D9</f>
-        <v>Lead time</v>
-      </c>
-      <c r="K5" s="26" t="str">
+        <v>Capacity factor</v>
+      </c>
+      <c r="M5" s="26" t="str">
         <f>Titles!$D10</f>
-        <v xml:space="preserve">Efficiency </v>
-      </c>
-      <c r="L5" s="26" t="str">
+        <v>Baseline capacity</v>
+      </c>
+      <c r="N5" s="26" t="str">
         <f>Titles!$D11</f>
-        <v>Capacity factor</v>
-      </c>
-      <c r="M5" s="26" t="str">
+        <v xml:space="preserve">Capture/production rates  </v>
+      </c>
+      <c r="O5" s="26" t="str">
         <f>Titles!$D12</f>
-        <v>Baseline capacity</v>
-      </c>
-      <c r="N5" s="26" t="str">
+        <v>Eff learning</v>
+      </c>
+      <c r="P5" s="26" t="str">
         <f>Titles!$D13</f>
-        <v xml:space="preserve">Capture/production rates  </v>
-      </c>
-      <c r="O5" s="26" t="str">
+        <v>Inv learning</v>
+      </c>
+      <c r="Q5" s="26" t="str">
         <f>Titles!$D14</f>
-        <v>Eff learning</v>
-      </c>
-      <c r="P5" s="26" t="str">
-        <f>Titles!$D15</f>
-        <v>Inv learning</v>
-      </c>
-      <c r="Q5" s="26" t="str">
-        <f>Titles!$D16</f>
         <v>OPEX learning</v>
       </c>
     </row>
